--- a/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_Mouser.xlsx
+++ b/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_Mouser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\CanAssist\Altium\TSI_SAMP_SAMI\Project Outputs for TSI_SAMP_SAMI_V3.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53FC9992-CE8C-447D-94BE-F647063FBE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC583EC6-EFB9-4CCA-BA3D-E0E21045ACA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
+    <workbookView xWindow="-28515" yWindow="7800" windowWidth="28800" windowHeight="15345" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMI_V3.5" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Designator</t>
-  </si>
-  <si>
-    <t>Revision Status</t>
   </si>
   <si>
     <t>Quantity</t>
@@ -729,26 +726,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4DC37E-2EE5-40BA-BB89-F354D725F7F7}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="41.140625" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
-    <col min="12" max="12" width="20.85546875" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -788,107 +784,104 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
-        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="M2" s="1">
+        <v>15410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="M2" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="N2" s="1">
-        <v>15410</v>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="M3" s="1">
+        <v>225070</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="N3" s="1">
-        <v>225070</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1">
-        <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>33</v>
@@ -897,82 +890,80 @@
         <v>34</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>36</v>
+      <c r="K4" s="1">
+        <v>0.83</v>
       </c>
       <c r="L4" s="1">
         <v>0.83</v>
       </c>
       <c r="M4" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="N4" s="1">
         <v>8212</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="L5" s="1">
+        <v>5.07</v>
+      </c>
+      <c r="M5" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="M5" s="1">
-        <v>5.07</v>
-      </c>
-      <c r="N5" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
-        <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>46</v>
@@ -981,208 +972,203 @@
         <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>49</v>
+      <c r="K6" s="1">
+        <v>0.51</v>
       </c>
       <c r="L6" s="1">
         <v>0.51</v>
       </c>
       <c r="M6" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="N6" s="1">
         <v>3760</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>54</v>
+      <c r="K7" s="1">
+        <v>2.78</v>
       </c>
       <c r="L7" s="1">
         <v>2.78</v>
       </c>
       <c r="M7" s="1">
-        <v>2.78</v>
-      </c>
-      <c r="N7" s="1">
         <v>4687</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>58</v>
+      <c r="K8" s="1">
+        <v>1.4</v>
       </c>
       <c r="L8" s="1">
         <v>1.4</v>
       </c>
       <c r="M8" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="N8" s="1">
         <v>15227</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>65</v>
+      <c r="K9" s="1">
+        <v>0.1</v>
       </c>
       <c r="L9" s="1">
         <v>0.1</v>
       </c>
       <c r="M9" s="1">
+        <v>40267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="1">
         <v>0.1</v>
-      </c>
-      <c r="N9" s="1">
-        <v>40267</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="L10" s="1">
         <v>0.1</v>
       </c>
       <c r="M10" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="N10" s="1">
         <v>58506</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1">
-        <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>74</v>
@@ -1191,156 +1177,150 @@
         <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>77</v>
+      <c r="K11" s="1">
+        <v>0.72</v>
       </c>
       <c r="L11" s="1">
         <v>0.72</v>
       </c>
       <c r="M11" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="N11" s="1">
         <v>4220</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>83</v>
+      <c r="K12" s="1">
+        <v>12.95</v>
       </c>
       <c r="L12" s="1">
         <v>12.95</v>
       </c>
       <c r="M12" s="1">
-        <v>12.95</v>
-      </c>
-      <c r="N12" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>88</v>
+      <c r="K13" s="1">
+        <v>12.5</v>
       </c>
       <c r="L13" s="1">
         <v>12.5</v>
       </c>
       <c r="M13" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="N13" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
       <c r="F14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>94</v>
+      <c r="K14" s="1">
+        <v>2.0699999999999998</v>
       </c>
       <c r="L14" s="1">
         <v>2.0699999999999998</v>
       </c>
       <c r="M14" s="1">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="N14" s="1">
         <v>2068</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N14">
-    <sortCondition ref="J2:J14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M14">
+    <sortCondition ref="I2:I14"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
